--- a/projects/ai-core/doc/data/res_syn_pe_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pe_area.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
-  <si>
-    <t xml:space="preserve">Intra-PE Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane-A BFP, ASAP7 RVT/TT (boundary-preserved synthesis)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">Intra-PE Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane-A BFP, ASAP7 RVT/TT (boundary-preserved synthesis) / NR4SD BFP</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -104,19 +104,13 @@
     <t xml:space="preserve">Bit-Plane-B BFP total </t>
   </si>
   <si>
-    <t xml:space="preserve">Standalone dot-product cores — cross-check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dp_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dp_8_sqr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dp_8_bpl_a_bfp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dp_8_bpl_b_bfp</t>
+    <t xml:space="preserve">NR4SD BFP — pe_nr4sd_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP8-Array (16 × dp_8_nr4sd_bfp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR4SD BFP total </t>
   </si>
 </sst>
 </file>
@@ -380,13 +374,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H50"/>
+  <dimension ref="B2:H1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="23.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="36.26"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="9" style="1" width="8.67"/>
   </cols>
   <sheetData>
@@ -1149,7 +1142,7 @@
         <v>1.20141049998703</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
         <v>27</v>
       </c>
@@ -1160,7 +1153,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="n">
         <v>1</v>
       </c>
@@ -1168,84 +1161,115 @@
         <v>28</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>202.414</v>
+        <v>147.123135</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>202.414</v>
-      </c>
-      <c r="G47" s="5"/>
+        <v>2353.97016</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>0.44768562293941</v>
+      </c>
       <c r="H47" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.546557729287753</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>129.427</v>
+        <v>1698.32214</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>129.427</v>
-      </c>
-      <c r="G48" s="5"/>
+        <v>1698.32214</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>0.322992371830955</v>
+      </c>
       <c r="H48" s="8" t="n">
-        <v>0.639417233985792</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.394325768529503</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>190.6335</v>
+        <v>860.77404</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>190.6335</v>
-      </c>
-      <c r="G49" s="9"/>
+        <v>860.77404</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>0.163704777934599</v>
+      </c>
       <c r="H49" s="8" t="n">
-        <v>0.941799974310077</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.199859247464822</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="n">
         <v>4</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>120.198</v>
+        <v>345.02112</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>120.198</v>
-      </c>
-      <c r="G50" s="9"/>
+        <v>345.02112</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>0.0656172272950362</v>
+      </c>
       <c r="H50" s="8" t="n">
-        <v>0.593822561680516</v>
-      </c>
-    </row>
+        <v>0.0801088998951105</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="11" t="n">
+        <v>5258.08746</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>1.22085164517719</v>
+      </c>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B9:E9"/>
@@ -1260,6 +1284,7 @@
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B51:E51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
